--- a/target/test-classes/com/automation/tests/BusinessFlow.xlsx
+++ b/target/test-classes/com/automation/tests/BusinessFlow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tutru\Downloads\JiraTest\SeleniumJavaAllureHybrid-main\src\test\java\com\automation\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABBFC50-69C8-4546-919F-C0B330A81342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A099E9-9622-47C2-92F8-04E4568D2811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="599" activeTab="2" xr2:uid="{E675EAC9-22E1-4F1A-A167-77A0AB850349}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="599" xr2:uid="{E675EAC9-22E1-4F1A-A167-77A0AB850349}"/>
   </bookViews>
   <sheets>
     <sheet name="BusinessFlow" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="550">
   <si>
     <t>TestCase</t>
   </si>
@@ -1807,6 +1807,15 @@
   </si>
   <si>
     <t>sauce mobile</t>
+  </si>
+  <si>
+    <t>XSP-61</t>
+  </si>
+  <si>
+    <t>XSP-62</t>
+  </si>
+  <si>
+    <t>XSP-3</t>
   </si>
 </sst>
 </file>
@@ -2977,39 +2986,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C027A1-095F-4F98-9B33-A1114ADD003F}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.21875" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.109375" customWidth="1"/>
-    <col min="10" max="10" width="15.88671875" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="67" t="s">
         <v>536</v>
       </c>
       <c r="B1" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67" t="s">
         <v>541</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="E1" s="67" t="s">
         <v>538</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>542</v>
       </c>
       <c r="F1" s="67" t="s">
         <v>542</v>
@@ -3017,150 +3024,168 @@
       <c r="G1" s="67" t="s">
         <v>542</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="67" t="s">
+        <v>542</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="B2" s="68" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="68" t="s">
+        <v>548</v>
+      </c>
+      <c r="D2" s="68" t="s">
         <v>537</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="E2" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="F2" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="F2" s="68"/>
       <c r="G2" s="68"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="4"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="7"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="68" t="s">
         <v>529</v>
       </c>
       <c r="B3" s="68" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C3" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D3" s="68" t="s">
         <v>537</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="E3" s="68" t="s">
         <v>546</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="F3" s="68" t="s">
         <v>545</v>
       </c>
-      <c r="F3" s="68"/>
       <c r="G3" s="68"/>
-    </row>
-    <row r="4" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="68"/>
+    </row>
+    <row r="4" spans="1:15" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="68" t="s">
         <v>530</v>
       </c>
       <c r="B4" s="68" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C4" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D4" s="68" t="s">
         <v>537</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="E4" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="F4" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="F4" s="68"/>
       <c r="G4" s="68"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="4"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="7"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="68" t="s">
         <v>531</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C5" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D5" s="68" t="s">
         <v>537</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="E5" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="F5" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="F5" s="68"/>
       <c r="G5" s="68"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="4"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="7"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="68" t="s">
         <v>532</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C6" s="68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D6" s="68" t="s">
         <v>537</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="E6" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="F6" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="F6" s="68"/>
       <c r="G6" s="68"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="4"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
